--- a/artfynd/A 6307-2023 artfynd.xlsx
+++ b/artfynd/A 6307-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6307-2023 artfynd.xlsx
+++ b/artfynd/A 6307-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97356826</v>
+        <v>97356873</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479552.7736983081</v>
+        <v>479552</v>
       </c>
       <c r="R2" t="n">
-        <v>6438513.885990261</v>
+        <v>6438519</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-09-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,50 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97356873</v>
+        <v>97356960</v>
       </c>
       <c r="B3" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>990</v>
+        <v>4769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ca 700 m sydost om Sutarp, Sm</t>
+          <t>ca 700 m SO om Sutarp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479551.7387740698</v>
+        <v>479552</v>
       </c>
       <c r="R3" t="n">
-        <v>6438518.649639724</v>
+        <v>6438500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2021-09-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -906,6 +876,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97356826</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ca 700 m sydost om Sutarp, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>479553</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6438514</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tranås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Adelöv</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>NVI inventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6307-2023 artfynd.xlsx
+++ b/artfynd/A 6307-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356873</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356960</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97356826</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>